--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_395_R43.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_395_R43.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8996</v>
+        <v>2.3342</v>
       </c>
       <c r="E2" t="n">
-        <v>3.368</v>
+        <v>3.6733</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4684</v>
+        <v>-1.3391</v>
       </c>
       <c r="G2" t="n">
         <v>1.7711</v>
@@ -610,13 +610,13 @@
         <v>1.5923</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.437</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1435</v>
+        <v>0.1618</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.728</v>
+        <v>-0.5987</v>
       </c>
       <c r="V2" t="n">
         <v>0.5451</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7167</v>
+        <v>1.8281</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8091</v>
+        <v>2.1144</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0924</v>
+        <v>-0.2863</v>
       </c>
       <c r="G3" t="n">
         <v>0.122</v>
@@ -688,13 +688,13 @@
         <v>1.5923</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0024</v>
+        <v>0.1137</v>
       </c>
       <c r="T3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.3773</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0696</v>
+        <v>-0.2635</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0155</v>
+        <v>0.2503</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9432</v>
+        <v>1.1767</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9587</v>
+        <v>-0.9263</v>
       </c>
       <c r="G4" t="n">
         <v>0.0348</v>
@@ -766,13 +766,13 @@
         <v>0.4549</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5052</v>
+        <v>-0.2394</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2155</v>
+        <v>0.018</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2897</v>
+        <v>-0.2574</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0446</v>
+        <v>0.1139</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7012</v>
+        <v>-1.2159</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7459</v>
+        <v>1.3298</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5437</v>
+        <v>0.2519</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0019</v>
+        <v>0.0896</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5455</v>
+        <v>0.1623</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3215</v>
+        <v>0.7163</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4665</v>
+        <v>0.9316</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1449</v>
+        <v>-0.2154</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8652</v>
+        <v>-0.4644</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4646</v>
+        <v>-0.842</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4006</v>
+        <v>0.3777</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4549</v>
+        <v>-2.2747</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.4121</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4549</v>
+        <v>1.1374</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5891</v>
+        <v>-0.6585</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7664</v>
+        <v>-0.7003</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1773</v>
+        <v>0.0417</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5451</v>
+        <v>2.7953</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3867</v>
+        <v>2.1802</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1583</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1519</v>
+        <v>-0.1968</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4494</v>
+        <v>0.3278</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2975</v>
+        <v>-0.5246</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2519</v>
+        <v>3.4294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0896</v>
+        <v>-1.4492</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1623</v>
+        <v>4.8786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7163</v>
+        <v>4.5838</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9316</v>
+        <v>-0.0727</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2154</v>
+        <v>4.6566</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4644</v>
+        <v>-1.1545</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.842</v>
+        <v>-1.3765</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3777</v>
+        <v>0.222</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2747</v>
+        <v>-2.5022</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.4121</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1374</v>
+        <v>0.9099</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9243</v>
+        <v>-1.0356</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9337</v>
+        <v>-0.8439</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0094</v>
+        <v>-0.1917</v>
       </c>
       <c r="V6" t="n">
-        <v>2.7953</v>
+        <v>-0.0883</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6151</v>
+        <v>-0.0883</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5403</v>
+        <v>-0.4757</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9419999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4017</v>
+        <v>0.4663</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4996</v>
@@ -1000,13 +1000,13 @@
         <v>0.6824</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7231</v>
+        <v>-0.6585</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2155</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5077</v>
+        <v>-0.443</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7325</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.8841</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8478</v>
+        <v>-1.6166</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4294</v>
+        <v>-0.5437</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4492</v>
+        <v>0.0019</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8786</v>
+        <v>-0.5455</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5838</v>
+        <v>1.3215</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0727</v>
+        <v>1.4665</v>
       </c>
       <c r="L8" t="n">
-        <v>4.6566</v>
+        <v>-0.1449</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1545</v>
+        <v>-1.8652</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3765</v>
+        <v>-1.4646</v>
       </c>
       <c r="O8" t="n">
-        <v>0.222</v>
+        <v>-0.4006</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5022</v>
+        <v>0.4549</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4121</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9099</v>
+        <v>0.4549</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5923</v>
+        <v>-0.0987</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0774</v>
+        <v>-0.0508</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5149</v>
+        <v>-0.048</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0883</v>
+        <v>-0.5451</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3867</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0883</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8131</v>
+        <v>-1.0436</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6788</v>
+        <v>-0.181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8657</v>
+        <v>-0.8626</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3315</v>
+        <v>-0.7443</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.066</v>
+        <v>-0.3105</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3976</v>
+        <v>-0.4338</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3141</v>
+        <v>0.0345</v>
       </c>
       <c r="K9" t="n">
-        <v>1.016</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.298</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9825</v>
+        <v>-0.7788</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0821</v>
+        <v>-0.3451</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09950000000000001</v>
+        <v>-0.4338</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8198</v>
+        <v>0.2275</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4121</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5923</v>
+        <v>0.2275</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6752</v>
+        <v>-0.5268</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4192</v>
+        <v>-0.2155</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2559</v>
+        <v>-0.3113</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0436</v>
+        <v>-1.7863</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.181</v>
+        <v>0.2711</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8626</v>
+        <v>-2.0574</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7443</v>
+        <v>-3.0084</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3105</v>
+        <v>-1.501</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4338</v>
+        <v>-1.5074</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0345</v>
+        <v>0.0424</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0345</v>
+        <v>0.2206</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.1781</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7788</v>
+        <v>-3.0509</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3451</v>
+        <v>-1.7215</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4338</v>
+        <v>-1.3293</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2275</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5268</v>
+        <v>-0.1856</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2155</v>
+        <v>-0.2692</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3113</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.027</v>
+        <v>-1.8295</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0342</v>
+        <v>-2.3074</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9927</v>
+        <v>0.4779</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0084</v>
+        <v>0.3315</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.501</v>
+        <v>-0.066</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5074</v>
+        <v>0.3976</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0424</v>
+        <v>1.3141</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2206</v>
+        <v>1.016</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1781</v>
+        <v>0.298</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0509</v>
+        <v>-0.9825</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7215</v>
+        <v>-1.0821</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3293</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2275</v>
+        <v>-1.8198</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1374</v>
+        <v>-3.4121</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9099</v>
+        <v>1.5923</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4262</v>
+        <v>-0.3413</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5745</v>
+        <v>-0.2093</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1483</v>
+        <v>-0.1319</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5738</v>
+        <v>-3.4499</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9016</v>
+        <v>-2.713</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6722</v>
+        <v>-0.7369</v>
       </c>
       <c r="G12" t="n">
         <v>-5.5424</v>
@@ -1390,13 +1390,13 @@
         <v>1.8198</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6657</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5745</v>
+        <v>-0.3859</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0912</v>
+        <v>-0.1559</v>
       </c>
       <c r="V12" t="n">
         <v>1.9519</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.347</v>
+        <v>-4.987799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7287999999999992</v>
+        <v>1.088099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.075799999999999</v>
+        <v>-6.0758</v>
       </c>
       <c r="G13" t="n">
         <v>-4.397699999999999</v>
@@ -1438,13 +1438,13 @@
         <v>-4.3973</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="J13" t="n">
         <v>11.1442</v>
       </c>
       <c r="K13" t="n">
-        <v>7.304300000000001</v>
+        <v>7.3043</v>
       </c>
       <c r="L13" t="n">
         <v>3.839900000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-11.702</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.839999999999999</v>
+        <v>-3.84</v>
       </c>
       <c r="P13" t="n">
         <v>-2.274900000000001</v>
@@ -1468,10 +1468,10 @@
         <v>11.3736</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.9684</v>
+        <v>-4.609500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.6925</v>
+        <v>-2.3333</v>
       </c>
       <c r="U13" t="n">
         <v>-2.2761</v>
@@ -1480,16 +1480,16 @@
         <v>6.2941</v>
       </c>
       <c r="W13" t="n">
-        <v>5.9257</v>
+        <v>5.925700000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3684999999999999</v>
+        <v>0.3685</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8307</v>
+        <v>3.2252</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9615</v>
+        <v>4.0292</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8692</v>
+        <v>-0.8041</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5463</v>
+        <v>3.576</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1916</v>
+        <v>4.9875</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7379</v>
+        <v>-1.4115</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6931</v>
+        <v>4.9479</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7282999999999999</v>
+        <v>6.0865</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4214</v>
+        <v>-1.1386</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1468</v>
+        <v>-1.3719</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4632</v>
+        <v>-1.0989</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3164</v>
+        <v>-0.273</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2275</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3648</v>
+        <v>-1.5923</v>
       </c>
       <c r="R14" t="n">
         <v>1.5923</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8304</v>
+        <v>0.7393</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4067</v>
+        <v>0.6736</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4237</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7734</v>
+        <v>-1.0901</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.7734</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8968</v>
+        <v>2.922</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2121</v>
+        <v>0.7942</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3153</v>
+        <v>2.1278</v>
       </c>
       <c r="G15" t="n">
-        <v>3.576</v>
+        <v>1.5463</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9875</v>
+        <v>-1.1916</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4115</v>
+        <v>2.7379</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9479</v>
+        <v>1.6931</v>
       </c>
       <c r="K15" t="n">
-        <v>6.0865</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1386</v>
+        <v>2.4214</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3719</v>
+        <v>-0.1468</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0989</v>
+        <v>-0.4632</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.273</v>
+        <v>0.3164</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.2275</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5923</v>
+        <v>-1.3648</v>
       </c>
       <c r="R15" t="n">
         <v>1.5923</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.589</v>
+        <v>1.9216</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1435</v>
+        <v>1.2393</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4455</v>
+        <v>0.6823</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0901</v>
+        <v>-0.7734</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6451</v>
+        <v>2.1361</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5117</v>
+        <v>3.5837</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1334</v>
+        <v>-1.4476</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1995</v>
+        <v>0.4623</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3817</v>
+        <v>1.142</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1822</v>
+        <v>-0.6798</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1587</v>
+        <v>2.9275</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1079</v>
+        <v>1.4665</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2666</v>
+        <v>1.461</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3582</v>
+        <v>-2.4652</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2738</v>
+        <v>-0.3244</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0844</v>
+        <v>-2.1407</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3648</v>
+        <v>0.9099</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2275</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3648</v>
+        <v>1.1374</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4798</v>
+        <v>-0.3262</v>
       </c>
       <c r="T16" t="n">
-        <v>1.353</v>
+        <v>-0.2064</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1268</v>
+        <v>-0.1198</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2938</v>
+        <v>1.2092</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0.8791</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7062</v>
+        <v>0.3301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4623</v>
+        <v>0.7456</v>
       </c>
       <c r="H17" t="n">
-        <v>1.142</v>
+        <v>-0.102</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6798</v>
+        <v>0.8476</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9275</v>
+        <v>1.4088</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4665</v>
+        <v>0.6556</v>
       </c>
       <c r="L17" t="n">
-        <v>1.461</v>
+        <v>0.7532</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4652</v>
+        <v>-0.6632</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3244</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1407</v>
+        <v>0.0944</v>
       </c>
       <c r="P17" t="n">
         <v>0.9099</v>
@@ -1780,22 +1780,22 @@
         <v>1.1374</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1685</v>
+        <v>0.0988</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7901</v>
+        <v>-0.3022</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3784</v>
+        <v>0.401</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0901</v>
+        <v>-0.5451</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2846</v>
+        <v>1.1428</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4153</v>
+        <v>0.5321</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8693</v>
+        <v>0.6107</v>
       </c>
       <c r="G18" t="n">
         <v>1.5286</v>
@@ -1858,13 +1858,13 @@
         <v>0.4549</v>
       </c>
       <c r="S18" t="n">
-        <v>0.917</v>
+        <v>0.7752</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.7513</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2824</v>
+        <v>0.0238</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3885</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1894</v>
+        <v>1.0789</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7624</v>
+        <v>2.6522</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4271</v>
+        <v>-1.5732</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7456</v>
+        <v>4.6812</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.102</v>
+        <v>2.0883</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8476</v>
+        <v>2.5929</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4088</v>
+        <v>4.828</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6556</v>
+        <v>2.5515</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7532</v>
+        <v>2.2765</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6632</v>
+        <v>-0.1468</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.4632</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0944</v>
+        <v>0.3164</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.5923</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.5022</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.9099</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.2275</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.1374</v>
-      </c>
       <c r="S19" t="n">
-        <v>0.079</v>
+        <v>0.7153</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.419</v>
+        <v>0.3264</v>
       </c>
       <c r="U19" t="n">
-        <v>0.498</v>
+        <v>0.3889</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5451</v>
+        <v>-2.7253</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5451</v>
+        <v>-2.7253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2678</v>
+        <v>0.6861</v>
       </c>
       <c r="E20" t="n">
-        <v>1.835</v>
+        <v>0.8113</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5673</v>
+        <v>-0.1252</v>
       </c>
       <c r="G20" t="n">
-        <v>4.6812</v>
+        <v>-1.1995</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0883</v>
+        <v>-1.3817</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5929</v>
+        <v>0.1822</v>
       </c>
       <c r="J20" t="n">
-        <v>4.828</v>
+        <v>0.1587</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5515</v>
+        <v>-1.1079</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2765</v>
+        <v>1.2666</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1468</v>
+        <v>-1.3582</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4632</v>
+        <v>-0.2738</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3164</v>
+        <v>-1.0844</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5923</v>
+        <v>1.3648</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5022</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0959</v>
+        <v>0.5208</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4908</v>
+        <v>0.6526</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3949</v>
+        <v>-0.1318</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.7253</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2432</v>
+        <v>-0.224</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0633</v>
+        <v>-2.2115</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.18</v>
+        <v>1.9875</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5315</v>
+        <v>-0.0204</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9181</v>
+        <v>1.5014</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-1.5218</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2789</v>
+        <v>0.7664</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3161</v>
+        <v>2.6378</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>-1.8714</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2526</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.602</v>
+        <v>-1.1364</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6506</v>
+        <v>0.3496</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9099</v>
+        <v>-1.1374</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.6396</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9099</v>
+        <v>2.5022</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3784</v>
+        <v>0.9338</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2156</v>
+        <v>-0.0417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1628</v>
+        <v>0.9755</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.7034</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.7034</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4515</v>
+        <v>-0.2953</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4449</v>
+        <v>-0.18</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9935</v>
+        <v>-0.1153</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0204</v>
+        <v>-1.5315</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5014</v>
+        <v>-0.9181</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5218</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7664</v>
+        <v>-0.2789</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6378</v>
+        <v>-0.3161</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8714</v>
+        <v>0.0373</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-1.2526</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1364</v>
+        <v>-0.602</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3496</v>
+        <v>-0.6506</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1374</v>
+        <v>0.9099</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6396</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5022</v>
+        <v>0.9099</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7063</v>
+        <v>0.3263</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2752</v>
+        <v>0.0989</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9815</v>
+        <v>0.2274</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7034</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1708</v>
+        <v>-1.9954</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3719</v>
+        <v>-2.2552</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2011</v>
+        <v>0.2598</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0161</v>
@@ -2248,13 +2248,13 @@
         <v>1.3648</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5196</v>
+        <v>-0.3442</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1372</v>
+        <v>-1.0205</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6176</v>
+        <v>0.6763</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1958</v>
+        <v>-3.7604</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7419</v>
+        <v>-2.5591</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4539</v>
+        <v>-1.2013</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3749</v>
@@ -2326,13 +2326,13 @@
         <v>0.6824</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9507</v>
+        <v>0.3862</v>
       </c>
       <c r="T24" t="n">
-        <v>0.922</v>
+        <v>0.1049</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0287</v>
+        <v>0.2813</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8617</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.3469</v>
+        <v>6.1252</v>
       </c>
       <c r="E25" t="n">
         <v>6.076000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7290999999999996</v>
+        <v>0.04920000000000035</v>
       </c>
       <c r="G25" t="n">
-        <v>4.397599999999999</v>
+        <v>4.397600000000001</v>
       </c>
       <c r="H25" t="n">
         <v>4.3976</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.0001000000000004331</v>
       </c>
       <c r="J25" t="n">
         <v>15.5419</v>
@@ -2383,7 +2383,7 @@
         <v>11.7021</v>
       </c>
       <c r="L25" t="n">
-        <v>3.8398</v>
+        <v>3.839799999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-11.1443</v>
@@ -2395,7 +2395,7 @@
         <v>-3.8399</v>
       </c>
       <c r="P25" t="n">
-        <v>2.274700000000001</v>
+        <v>2.2747</v>
       </c>
       <c r="Q25" t="n">
         <v>-11.3737</v>
@@ -2404,19 +2404,19 @@
         <v>13.6483</v>
       </c>
       <c r="S25" t="n">
-        <v>4.9686</v>
+        <v>5.7469</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2761</v>
+        <v>2.2762</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6925</v>
+        <v>3.470599999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-6.294</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3684000000000001</v>
+        <v>-0.3683999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-5.9256</v>
